--- a/src/data/raw/2016 შუალედური მაისი.xlsx
+++ b/src/data/raw/2016 შუალედური მაისი.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A70995-870B-4CDE-ADF4-CBFF70BA4715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FAC26A-0B84-47CE-B40A-E469AA4B7E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="შედეგები" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="90">
   <si>
     <t>ჯამი:</t>
   </si>
@@ -81,12 +81,6 @@
   </si>
   <si>
     <t>23.05.2016</t>
-  </si>
-  <si>
-    <t>გადათვალეს 23-ში</t>
-  </si>
-  <si>
-    <t>გადათვალეს 24-ში</t>
   </si>
   <si>
     <t>vote_1</t>
@@ -835,6 +829,9 @@
       </rPr>
       <t>ლაგვილავა</t>
     </r>
+  </si>
+  <si>
+    <t>maj_id</t>
   </si>
 </sst>
 </file>
@@ -988,7 +985,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1050,6 +1047,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1378,7 +1377,7 @@
     <col min="21" max="16384" width="9.07421875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
@@ -1410,19 +1409,19 @@
         <v>9</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="P1" s="7">
         <v>42</v>
@@ -1439,8 +1438,11 @@
       <c r="T1" s="14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U1" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A2" s="5">
         <v>10</v>
       </c>
@@ -1497,8 +1499,11 @@
       <c r="T2" s="10">
         <v>0.91666666666666663</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U2" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>10</v>
       </c>
@@ -1555,8 +1560,11 @@
       <c r="T3" s="10">
         <v>0.89930555555555547</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U3" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A4" s="5">
         <v>10</v>
       </c>
@@ -1611,8 +1619,11 @@
         <v>14</v>
       </c>
       <c r="T4" s="10"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U4" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <v>10</v>
       </c>
@@ -1669,8 +1680,11 @@
       <c r="T5" s="10">
         <v>0.90208333333333324</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U5" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A6" s="5">
         <v>10</v>
       </c>
@@ -1727,8 +1741,11 @@
       <c r="T6" s="10">
         <v>0.90625</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U6" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -1785,8 +1802,11 @@
       <c r="T7" s="10">
         <v>0.8666666666666667</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U7" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -1843,8 +1863,11 @@
       <c r="T8" s="10">
         <v>0.89583333333333337</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U8" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <v>10</v>
       </c>
@@ -1901,8 +1924,11 @@
       <c r="T9" s="10">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U9" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A10" s="5">
         <v>10</v>
       </c>
@@ -1959,8 +1985,11 @@
       <c r="T10" s="10">
         <v>0.89583333333333337</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U10" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2017,8 +2046,11 @@
       <c r="T11" s="10">
         <v>0.88402777777777775</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U11" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -2075,8 +2107,11 @@
       <c r="T12" s="10">
         <v>0.90833333333333333</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U12" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2133,8 +2168,11 @@
       <c r="T13" s="10">
         <v>0.90416666666666667</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U13" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A14" s="5">
         <v>10</v>
       </c>
@@ -2191,8 +2229,11 @@
       <c r="T14" s="10">
         <v>0.88958333333333339</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U14" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -2249,8 +2290,11 @@
       <c r="T15" s="10">
         <v>0.89097222222222217</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U15" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A16" s="5">
         <v>10</v>
       </c>
@@ -2307,8 +2351,11 @@
       <c r="T16" s="10">
         <v>0.89583333333333337</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U16" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -2365,8 +2412,11 @@
       <c r="T17" s="10">
         <v>0.89583333333333337</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U17" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A18" s="5">
         <v>10</v>
       </c>
@@ -2423,8 +2473,11 @@
       <c r="T18" s="10">
         <v>0.8979166666666667</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U18" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <v>10</v>
       </c>
@@ -2481,8 +2534,11 @@
       <c r="T19" s="10">
         <v>0.86805555555555547</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U19" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A20" s="5">
         <v>10</v>
       </c>
@@ -2539,8 +2595,11 @@
       <c r="T20" s="10">
         <v>0.87916666666666676</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U20" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <v>10</v>
       </c>
@@ -2597,8 +2656,11 @@
       <c r="T21" s="10">
         <v>0.88750000000000007</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U21" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A22" s="5">
         <v>10</v>
       </c>
@@ -2655,8 +2717,11 @@
       <c r="T22" s="10">
         <v>0.9375</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U22" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
         <v>10</v>
       </c>
@@ -2713,8 +2778,11 @@
       <c r="T23" s="10">
         <v>0.90138888888888891</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U23" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A24" s="5">
         <v>10</v>
       </c>
@@ -2771,8 +2839,11 @@
       <c r="T24" s="10">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U24" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
         <v>10</v>
       </c>
@@ -2829,8 +2900,11 @@
       <c r="T25" s="10">
         <v>0.86458333333333337</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U25" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A26" s="5">
         <v>10</v>
       </c>
@@ -2887,8 +2961,11 @@
       <c r="T26" s="10">
         <v>0.87847222222222221</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U26" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
         <v>10</v>
       </c>
@@ -2945,8 +3022,11 @@
       <c r="T27" s="10">
         <v>0.91875000000000007</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="U27" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A28" s="7">
         <v>10</v>
       </c>
@@ -3000,8 +3080,11 @@
       </c>
       <c r="S28" s="11"/>
       <c r="T28" s="12"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U28" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
         <v>21</v>
       </c>
@@ -3060,8 +3143,11 @@
       <c r="T29" s="10">
         <v>0.92847222222222225</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U29" s="2">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <v>21</v>
       </c>
@@ -3120,8 +3206,11 @@
       <c r="T30" s="10">
         <v>0.92708333333333337</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U30" s="2">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -3180,8 +3269,11 @@
       <c r="T31" s="10">
         <v>0.90208333333333324</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="U31" s="2">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A32" s="7">
         <v>21</v>
       </c>
@@ -3247,6 +3339,9 @@
       </c>
       <c r="S32" s="9"/>
       <c r="T32" s="10"/>
+      <c r="U32" s="2">
+        <v>2108</v>
+      </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
@@ -3303,6 +3398,9 @@
       <c r="T33" s="10">
         <v>0.8965277777777777</v>
       </c>
+      <c r="U33" s="2">
+        <v>2118</v>
+      </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A34" s="1">
@@ -3358,6 +3456,9 @@
       </c>
       <c r="T34" s="10">
         <v>0.90625</v>
+      </c>
+      <c r="U34" s="2">
+        <v>2118</v>
       </c>
     </row>
     <row r="35" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
@@ -3420,6 +3521,9 @@
       </c>
       <c r="S35" s="11"/>
       <c r="T35" s="12"/>
+      <c r="U35" s="2">
+        <v>2118</v>
+      </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A36" s="1">
@@ -3478,8 +3582,8 @@
       <c r="T36" s="10">
         <v>0.9902777777777777</v>
       </c>
-      <c r="U36" s="2" t="s">
-        <v>18</v>
+      <c r="U36" s="2">
+        <v>3012</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.5">
@@ -3539,6 +3643,9 @@
       <c r="T37" s="10">
         <v>0.92499999999999993</v>
       </c>
+      <c r="U37" s="2">
+        <v>3012</v>
+      </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A38" s="1">
@@ -3596,6 +3703,9 @@
       </c>
       <c r="T38" s="10">
         <v>0.92986111111111114</v>
+      </c>
+      <c r="U38" s="2">
+        <v>3012</v>
       </c>
     </row>
     <row r="39" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
@@ -3654,6 +3764,9 @@
       </c>
       <c r="S39" s="11"/>
       <c r="T39" s="12"/>
+      <c r="U39" s="2">
+        <v>3012</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A40" s="1">
@@ -3712,6 +3825,9 @@
       <c r="T40" s="10">
         <v>0.97222222222222221</v>
       </c>
+      <c r="U40" s="2">
+        <v>5817</v>
+      </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A41" s="1">
@@ -3770,6 +3886,9 @@
       <c r="T41" s="10">
         <v>0.96111111111111114</v>
       </c>
+      <c r="U41" s="2">
+        <v>5817</v>
+      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A42" s="1">
@@ -3828,6 +3947,9 @@
       <c r="T42" s="10">
         <v>0.9375</v>
       </c>
+      <c r="U42" s="2">
+        <v>5817</v>
+      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A43" s="1">
@@ -3886,6 +4008,9 @@
       <c r="T43" s="10">
         <v>0.95486111111111116</v>
       </c>
+      <c r="U43" s="2">
+        <v>5817</v>
+      </c>
     </row>
     <row r="44" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A44" s="7">
@@ -3941,6 +4066,9 @@
       </c>
       <c r="S44" s="11"/>
       <c r="T44" s="12"/>
+      <c r="U44" s="2">
+        <v>5817</v>
+      </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A45" s="1">
@@ -3997,6 +4125,9 @@
       <c r="T45" s="10">
         <v>0.99652777777777779</v>
       </c>
+      <c r="U45" s="2">
+        <v>60104</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A46" s="1">
@@ -4052,6 +4183,9 @@
       </c>
       <c r="T46" s="10">
         <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="U46" s="2">
+        <v>60104</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.5">
@@ -4114,6 +4248,9 @@
       </c>
       <c r="S47" s="9"/>
       <c r="T47" s="10"/>
+      <c r="U47" s="2">
+        <v>60104</v>
+      </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A48" s="1">
@@ -4170,6 +4307,9 @@
       <c r="T48" s="10">
         <v>0.9555555555555556</v>
       </c>
+      <c r="U48" s="2">
+        <v>6005</v>
+      </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A49" s="1">
@@ -4225,6 +4365,9 @@
       </c>
       <c r="T49" s="10">
         <v>0.9604166666666667</v>
+      </c>
+      <c r="U49" s="2">
+        <v>6005</v>
       </c>
     </row>
     <row r="50" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
@@ -4287,6 +4430,9 @@
       </c>
       <c r="S50" s="11"/>
       <c r="T50" s="12"/>
+      <c r="U50" s="2">
+        <v>6005</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A51" s="1">
@@ -4341,6 +4487,9 @@
       <c r="T51" s="10">
         <v>0.86111111111111116</v>
       </c>
+      <c r="U51" s="2">
+        <v>6617</v>
+      </c>
     </row>
     <row r="52" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A52" s="7">
@@ -4391,6 +4540,9 @@
       </c>
       <c r="S52" s="11"/>
       <c r="T52" s="12"/>
+      <c r="U52" s="2">
+        <v>6617</v>
+      </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.5">
       <c r="A53" s="1">
@@ -4449,8 +4601,8 @@
       <c r="T53" s="10">
         <v>0.12083333333333333</v>
       </c>
-      <c r="U53" s="2" t="s">
-        <v>17</v>
+      <c r="U53" s="2">
+        <v>6715</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.5">
@@ -4510,8 +4662,8 @@
       <c r="T54" s="10">
         <v>0.92152777777777783</v>
       </c>
-      <c r="U54" s="2" t="s">
-        <v>17</v>
+      <c r="U54" s="2">
+        <v>6715</v>
       </c>
     </row>
     <row r="55" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.5">
@@ -4568,6 +4720,9 @@
       </c>
       <c r="S55" s="11"/>
       <c r="T55" s="12"/>
+      <c r="U55" s="2">
+        <v>6715</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.25" header="0.25" footer="0"/>
@@ -4580,7 +4735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB27E10E-F33F-4A74-8C1F-F3126D5B8D0B}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.84375" bestFit="1" customWidth="1"/>
@@ -4590,37 +4745,41 @@
     <col min="5" max="5" width="69.61328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.15234375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.23046875" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H1" s="25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A2" s="15">
         <v>10</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" s="16">
         <v>10.220000000000001</v>
@@ -4629,21 +4788,24 @@
         <v>24</v>
       </c>
       <c r="E2" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H2" s="26">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A3" s="15">
         <v>10</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="16">
         <v>10.220000000000001</v>
@@ -4652,21 +4814,24 @@
         <v>1</v>
       </c>
       <c r="E3" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H3" s="26">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A4" s="15">
         <v>10</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" s="16">
         <v>10.220000000000001</v>
@@ -4675,21 +4840,24 @@
         <v>41</v>
       </c>
       <c r="E4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H4" s="26">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A5" s="15">
         <v>21</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" s="16">
         <v>21.08</v>
@@ -4698,21 +4866,24 @@
         <v>24</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+      <c r="H5" s="26">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A6" s="15">
         <v>21</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="16">
         <v>21.08</v>
@@ -4721,21 +4892,24 @@
         <v>1</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+      <c r="H6" s="26">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A7" s="15">
         <v>21</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="16">
         <v>21.08</v>
@@ -4744,21 +4918,24 @@
         <v>41</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+      <c r="H7" s="26">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A8" s="15">
         <v>21</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="16">
         <v>21.08</v>
@@ -4767,21 +4944,24 @@
         <v>42</v>
       </c>
       <c r="E8" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H8" s="26">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A9" s="15">
         <v>21</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="16">
         <v>21.18</v>
@@ -4790,21 +4970,24 @@
         <v>1</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="H9" s="26">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A10" s="15">
         <v>21</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="16">
         <v>21.18</v>
@@ -4813,21 +4996,24 @@
         <v>41</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="H10" s="26">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A11" s="15">
         <v>30</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" s="16">
         <v>30.12</v>
@@ -4836,21 +5022,24 @@
         <v>24</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+      <c r="H11" s="26">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A12" s="15">
         <v>30</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="16">
         <v>30.12</v>
@@ -4859,21 +5048,24 @@
         <v>5</v>
       </c>
       <c r="E12" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H12" s="26">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A13" s="15">
         <v>30</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13" s="16">
         <v>30.12</v>
@@ -4882,21 +5074,24 @@
         <v>41</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+      <c r="H13" s="26">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A14" s="15">
         <v>58</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="16">
         <v>58.17</v>
@@ -4905,21 +5100,24 @@
         <v>41</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+      <c r="H14" s="26">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A15" s="15">
         <v>58</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C15" s="16">
         <v>58.17</v>
@@ -4928,21 +5126,24 @@
         <v>5</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+      <c r="H15" s="26">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A16" s="15">
         <v>58</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16" s="16">
         <v>58.17</v>
@@ -4951,21 +5152,24 @@
         <v>33</v>
       </c>
       <c r="E16" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H16" s="26">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A17" s="15">
         <v>60</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" s="17">
         <v>58444</v>
@@ -4974,21 +5178,24 @@
         <v>42</v>
       </c>
       <c r="E17" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+      <c r="H17" s="26">
+        <v>60104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A18" s="15">
         <v>60</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" s="17">
         <v>58444</v>
@@ -4997,21 +5204,24 @@
         <v>41</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+      <c r="H18" s="26">
+        <v>60104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A19" s="15">
         <v>60</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" s="16">
         <v>60.05</v>
@@ -5020,21 +5230,24 @@
         <v>5</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+      <c r="H19" s="26">
+        <v>6005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A20" s="15">
         <v>60</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="16">
         <v>60.05</v>
@@ -5043,21 +5256,24 @@
         <v>41</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+      <c r="H20" s="26">
+        <v>6005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A21" s="15">
         <v>66</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C21" s="16">
         <v>66.17</v>
@@ -5066,21 +5282,24 @@
         <v>41</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+      <c r="H21" s="26">
+        <v>6617</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A22" s="15">
         <v>67</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" s="16">
         <v>67.150000000000006</v>
@@ -5089,21 +5308,24 @@
         <v>1</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+      <c r="H22" s="26">
+        <v>6715</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A23" s="15">
         <v>67</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="16">
         <v>67.150000000000006</v>
@@ -5112,21 +5334,24 @@
         <v>5</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.9" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+      <c r="H23" s="26">
+        <v>6715</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A24" s="15">
         <v>67</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" s="16">
         <v>67.150000000000006</v>
@@ -5135,13 +5360,16 @@
         <v>41</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>90</v>
+        <v>88</v>
+      </c>
+      <c r="H24" s="26">
+        <v>6715</v>
       </c>
     </row>
   </sheetData>
